--- a/docs/01. 분석 - 사용자_요구사항_정의서.xlsx
+++ b/docs/01. 분석 - 사용자_요구사항_정의서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11013"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9523f8246e06aad/Data/프로젝트/제출문서양식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imjonghyeon/Documents/ses/ses_project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_6A9B258DE77BD0CD05E406E0F5E7AA6AF7AAE7FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30DBAE3E-2CC4-4FA4-B6ED-76F3DB482116}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4CA7A9-A051-E245-ACDE-7BDAF8F7CDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="3" r:id="rId1"/>
@@ -24,20 +24,20 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'사용자 요구사항 정의서'!$A$1:$J$9</definedName>
     <definedName name="병">INDIRECT([1]자료!$B1)</definedName>
     <definedName name="분류">[2]워크자료!$A$2:$A$65536</definedName>
     <definedName name="찾기분류">INDIRECT([2]자료!$B1)</definedName>
     <definedName name="최">[1]워크자료!$A$2:$A$65536</definedName>
     <definedName name="최병">INDIRECT([1]자료!$B1)</definedName>
     <definedName name="최병호">INDIRECT([3]자료!$B1)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'사용자 요구사항 정의서'!$A$1:$J$56</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="287">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -141,10 +141,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>홍길동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>조</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -267,28 +263,705 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>00기 0반 0조</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>M_001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>로그인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회원기능</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>○○ 시스템
+    <t>설문조사 플랫폼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임종현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 페이지 (로그인 전)</t>
+  </si>
+  <si>
+    <t>메인 페이지 (로그인 후)</t>
+  </si>
+  <si>
+    <t>로그인 페이지</t>
+  </si>
+  <si>
+    <t>설문조사 작성</t>
+  </si>
+  <si>
+    <t>설문조사 게시글 작성</t>
+  </si>
+  <si>
+    <t>설문조사 게시판</t>
+  </si>
+  <si>
+    <t>설문조사 상세 페이지</t>
+  </si>
+  <si>
+    <t>설문조사 폼(참여자)</t>
+  </si>
+  <si>
+    <t>공지사항</t>
+  </si>
+  <si>
+    <t>공지사항 상세 페이지</t>
+  </si>
+  <si>
+    <t>현금 인출</t>
+  </si>
+  <si>
+    <t>M_002</t>
+  </si>
+  <si>
+    <t>M_003</t>
+  </si>
+  <si>
+    <t>M_004</t>
+  </si>
+  <si>
+    <t>M_005</t>
+  </si>
+  <si>
+    <t>M_006</t>
+  </si>
+  <si>
+    <t>M_007</t>
+  </si>
+  <si>
+    <t>M_008</t>
+  </si>
+  <si>
+    <t>M_009</t>
+  </si>
+  <si>
+    <t>M_010</t>
+  </si>
+  <si>
+    <t>M_011</t>
+  </si>
+  <si>
+    <t>M_012</t>
+  </si>
+  <si>
+    <t>M_013</t>
+  </si>
+  <si>
+    <t>M_014</t>
+  </si>
+  <si>
+    <t>M_015</t>
+  </si>
+  <si>
+    <t>M_016</t>
+  </si>
+  <si>
+    <t>로그인 페이지 이동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 페이지 (로그인 전)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 페이지에서 로그인 페이지로 이동할 수 있어야 한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 요구사항</t>
+  </si>
+  <si>
+    <t>사용자 요구사항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>높음</t>
+  </si>
+  <si>
+    <t>높음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구현</t>
+  </si>
+  <si>
+    <t>구현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 이동 확인</t>
+  </si>
+  <si>
+    <t>페이지 이동 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원가입 페이지 이동</t>
+  </si>
+  <si>
+    <t>메인 페이지에서 회원가입 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>공지사항 페이지 이동</t>
+  </si>
+  <si>
+    <t>메인 페이지에서 공지사항 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>보통</t>
+  </si>
+  <si>
+    <t>설문조사 작성 이동</t>
+  </si>
+  <si>
+    <t>로그인 전에는 설문조사 작성을 누르면 로그인 페이지로 이동되어야 한다.</t>
+  </si>
+  <si>
+    <t>로그인 상태 확인 필요</t>
+  </si>
+  <si>
+    <t>설문조사 게시판 이동</t>
+  </si>
+  <si>
+    <t>메인 페이지에서 설문조사 게시판 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그아웃 기능</t>
+  </si>
+  <si>
+    <t>로그인 후, 사용자는 로그아웃을 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그아웃 확인</t>
+  </si>
+  <si>
+    <t>마이페이지 이동</t>
+  </si>
+  <si>
+    <t>로그인 후, 사용자는 마이페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그인 후, 사용자는 공지사항 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그인 후, 설문조사 작성 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그인 후, 설문조사 게시판 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>로그인 기능</t>
+  </si>
+  <si>
+    <t>로그인 페이지에서 사용자는 로그인을 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>유효한 사용자 정보 필요</t>
+  </si>
+  <si>
+    <t>로그인 성공 여부 확인</t>
+  </si>
+  <si>
+    <t>로그인 페이지에서 회원가입 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>회원가입 입력</t>
+  </si>
+  <si>
+    <t>회원가입 페이지</t>
+  </si>
+  <si>
+    <t>사용자는 아이디, 비밀번호, 비밀번호 확인, 이름, 생년월일, 성별, 핸드폰번호, 이메일을 입력할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>유효성 검사 필요</t>
+  </si>
+  <si>
+    <t>입력 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>이메일 인증</t>
+  </si>
+  <si>
+    <t>사용자는 이메일 인증을 통해 본인 확인을 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>이메일 서비스 연동 필요</t>
+  </si>
+  <si>
+    <t>이메일 인증 성공 확인</t>
+  </si>
+  <si>
+    <t>회원가입 제출</t>
+  </si>
+  <si>
+    <t>사용자는 회원가입 정보를 제출하여 계정을 생성할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>입력된 정보 유효성 확인 필요</t>
+  </si>
+  <si>
+    <t>회원가입 성공 여부 확인</t>
+  </si>
+  <si>
+    <t>회원가입 취소</t>
+  </si>
+  <si>
+    <t>사용자는 회원가입을 취소하고, 알림창을 통해 메인 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>취소 후 이동 확인</t>
+  </si>
+  <si>
+    <t>MP_001</t>
+  </si>
+  <si>
+    <t>프로필 수정 이동</t>
+  </si>
+  <si>
+    <t>마이페이지</t>
+  </si>
+  <si>
+    <t>마이페이지 기본값으로 프로필 수정 페이지로 이동하고, 암호 입력을 통해 인증을 받아야 한다.</t>
+  </si>
+  <si>
+    <t>인증 필요</t>
+  </si>
+  <si>
+    <t>프로필 수정 이동 확인</t>
+  </si>
+  <si>
+    <t>MP_001-1</t>
+  </si>
+  <si>
+    <t>회원 정보 수정</t>
+  </si>
+  <si>
+    <t>아이디, 이름, 생년월일, 성별을 제외한 정보(비밀번호, 연락처 등) 수정이 가능해야 한다.</t>
+  </si>
+  <si>
+    <t>아이디, 이름 등 일부 정보는 수정 불가</t>
+  </si>
+  <si>
+    <t>회원 정보 수정 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_001-2</t>
+  </si>
+  <si>
+    <t>회원 탈퇴</t>
+  </si>
+  <si>
+    <t>사용자는 마이페이지에서 회원 탈퇴를 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>회원 탈퇴 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_002</t>
+  </si>
+  <si>
+    <t>참여한 설문조사 확인</t>
+  </si>
+  <si>
+    <t>사용자는 참여한 설문조사 내역을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>참여 내역 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_003</t>
+  </si>
+  <si>
+    <t>작성한 설문조사 확인</t>
+  </si>
+  <si>
+    <t>사용자는 자신이 작성한 설문조사를 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>작성한 설문조사 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_003-1</t>
+  </si>
+  <si>
+    <t>참여 인원 확인</t>
+  </si>
+  <si>
+    <t>사용자는 자신이 작성한 설문조사에 대한 참여 인원을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>참여 인원 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_004</t>
+  </si>
+  <si>
+    <t>포인트 내역 확인</t>
+  </si>
+  <si>
+    <t>사용자는 마이페이지에서 포인트 내역을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>포인트 내역 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_005</t>
+  </si>
+  <si>
+    <t>결제 내역 확인</t>
+  </si>
+  <si>
+    <t>사용자는 마이페이지에서 결제 내역을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>결제 내역 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>MP_007</t>
+  </si>
+  <si>
+    <t>사용자는 보유 포인트를 현금으로 인출할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>인출 가능 포인트 필요</t>
+  </si>
+  <si>
+    <t>현금 인출 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SJ_001</t>
+  </si>
+  <si>
+    <t>날짜 설정</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사의 시작 및 종료 날짜를 설정할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>날짜 설정 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SJ_002</t>
+  </si>
+  <si>
+    <t>문항 추가</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사에 문항을 추가할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>문항 추가 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SJ_003</t>
+  </si>
+  <si>
+    <t>문항 삭제</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사에서 문항을 삭제할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>문항 삭제 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SJ_004</t>
+  </si>
+  <si>
+    <t>작성 완료</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사 작성을 완료할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>작성 완료 기능 확인</t>
+  </si>
+  <si>
+    <t>SJ_005</t>
+  </si>
+  <si>
+    <t>작성 취소</t>
+  </si>
+  <si>
+    <t>사용자는 작성 취소 버튼을 눌러 메인 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>작성 취소 후 페이지 이동 확인</t>
+  </si>
+  <si>
+    <t>SB_001</t>
+  </si>
+  <si>
+    <t>게시글 제목 입력</t>
+  </si>
+  <si>
+    <t>사용자는 게시글 제목을 입력할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>제목 입력 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SB_002</t>
+  </si>
+  <si>
+    <t>게시글 내용 입력</t>
+  </si>
+  <si>
+    <t>사용자는 게시글 내용을 입력할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>내용 입력 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SB_003</t>
+  </si>
+  <si>
+    <t>포인트 입력</t>
+  </si>
+  <si>
+    <t>사용자는 지급할 포인트를 입력할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>포인트 입력 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SB_004</t>
+  </si>
+  <si>
+    <t>공개/비공개 선택</t>
+  </si>
+  <si>
+    <t>사용자는 게시글을 공개 또는 비공개로 설정할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>공개 설정 확인</t>
+  </si>
+  <si>
+    <t>SB_004-1</t>
+  </si>
+  <si>
+    <t>비공개 암호 입력</t>
+  </si>
+  <si>
+    <t>사용자는 게시글을 비공개로 설정할 경우 암호를 입력할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>비공개 설정 필요</t>
+  </si>
+  <si>
+    <t>암호 입력 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>BP_001</t>
+  </si>
+  <si>
+    <t>게시글 이동</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사 게시글로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>게시글 이동 확인</t>
+  </si>
+  <si>
+    <t>BP_002</t>
+  </si>
+  <si>
+    <t>설문조사 검색</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사를 검색할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>검색 기능 확인</t>
+  </si>
+  <si>
+    <t>BP_003</t>
+  </si>
+  <si>
+    <t>카테고리 분류</t>
+  </si>
+  <si>
+    <t>사용자는 최대 3개의 카테고리를 선택하여 설문조사를 분류할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>최대 3개 선택 제한</t>
+  </si>
+  <si>
+    <t>카테고리 선택 확인</t>
+  </si>
+  <si>
+    <t>BP_004</t>
+  </si>
+  <si>
+    <t>다음 페이지 이동</t>
+  </si>
+  <si>
+    <t>사용자는 다음 페이지로 이동하여 게시글을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>BP_005</t>
+  </si>
+  <si>
+    <t>글쓰기 버튼</t>
+  </si>
+  <si>
+    <t>사용자는 '글쓰기' 버튼을 클릭하여 설문조사 폼 선택 페이지로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>SD_001</t>
+  </si>
+  <si>
+    <t>게시글 내용 확인</t>
+  </si>
+  <si>
+    <t>사용자는 게시글 내용을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>내용 확인 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SD_002</t>
+  </si>
+  <si>
+    <t>설문조사 폼 이동</t>
+  </si>
+  <si>
+    <t>사용자는 설문조사 폼으로 이동할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>폼 이동 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SD_003</t>
+  </si>
+  <si>
+    <t>댓글 작성</t>
+  </si>
+  <si>
+    <t>사용자는 댓글을 작성할 수 있어야 하며, 본인과 관리자만 댓글을 수정 및 삭제할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>댓글 권한 제한 필요</t>
+  </si>
+  <si>
+    <t>댓글 작성 및 수정 삭제 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SD_004</t>
+  </si>
+  <si>
+    <t>게시글 수정</t>
+  </si>
+  <si>
+    <t>작성자는 게시글을 수정할 수 있으나 설문조사 폼은 수정할 수 없다.</t>
+  </si>
+  <si>
+    <t>폼 수정 불가</t>
+  </si>
+  <si>
+    <t>게시글 수정 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SF_001</t>
+  </si>
+  <si>
+    <t>문항 선택</t>
+  </si>
+  <si>
+    <t>참여자는 설문조사 폼의 문항을 체크할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>문항 체크 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>SF_002</t>
+  </si>
+  <si>
+    <t>폼 제출</t>
+  </si>
+  <si>
+    <t>참여자는 설문조사 폼을 제출할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>폼 제출 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>NT_001</t>
+  </si>
+  <si>
+    <t>공지사항 게시글 열람</t>
+  </si>
+  <si>
+    <t>사용자는 공지사항 게시글을 클릭하여 내용을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>게시글 열람 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>NT_002</t>
+  </si>
+  <si>
+    <t>게시글 작성</t>
+  </si>
+  <si>
+    <t>관리자 유저는 공지사항 게시글을 작성할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>관리자 권한 필요</t>
+  </si>
+  <si>
+    <t>게시글 작성 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>NT_002-1</t>
+  </si>
+  <si>
+    <t>게시글 삭제</t>
+  </si>
+  <si>
+    <t>관리자 유저는 공지사항 게시글을 삭제할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>게시글 삭제 가능 여부 확인</t>
+  </si>
+  <si>
+    <t>NS_001</t>
+  </si>
+  <si>
+    <t>공지사항 내용 확인</t>
+  </si>
+  <si>
+    <t>사용자는 공지사항 게시글 내용을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>2024.10.29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 작성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13기 2조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임종현, 김수연, 전주영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문조사 플랫폼 시스템
 요구사항 정의서</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20xx.01.01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -296,7 +969,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -386,13 +1059,6 @@
     </font>
     <font>
       <b/>
-      <sz val="40"/>
-      <name val="바탕"/>
-      <family val="1"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="바탕"/>
       <family val="1"/>
@@ -433,8 +1099,62 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <name val="바탕"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,8 +1185,74 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -810,14 +1596,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -851,9 +1650,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -877,37 +1673,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -917,12 +1710,6 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -947,41 +1734,82 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1485,70 +2313,74 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.35" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.7890625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="10.41796875" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.41796875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="8.89453125" style="20"/>
-    <col min="5" max="8" width="11" style="20" customWidth="1"/>
-    <col min="9" max="16384" width="8.89453125" style="20"/>
+    <col min="1" max="1" width="20.83203125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" style="19" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="19"/>
+    <col min="5" max="8" width="11" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:8" ht="25" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="26" t="s">
+      <c r="C1" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="21">
+        <v>45594</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="25" customHeight="1" thickBot="1">
+      <c r="A2" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="C2" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="3" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:8" ht="381.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
+      <c r="E2" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1"/>
+    <row r="4" spans="1:8" ht="381.75" customHeight="1" thickBot="1">
+      <c r="A4" s="79" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1566,17 +2398,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.7890625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7890625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.7890625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.89453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.1015625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.89453125" style="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.1640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1584,17 +2416,17 @@
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:6" ht="21" x14ac:dyDescent="0.8">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:6" ht="20">
+      <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-    </row>
-    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" thickBot="1">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1602,7 +2434,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -1615,141 +2447,161 @@
       <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="37"/>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="15">
+      <c r="A5" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="36"/>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A6" s="4"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A7" s="4"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A8" s="4"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A9" s="4"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A10" s="4"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A11" s="4"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A12" s="4"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A13" s="4"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A14" s="4"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A15" s="4"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A16" s="4"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-    </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A17" s="4"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-    </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+    </row>
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A18" s="4"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-    </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" ht="15.35" x14ac:dyDescent="0.6">
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A19" s="4"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-    </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" ht="15.7" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
       <c r="A20" s="3"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E20:F20"/>
@@ -1758,16 +2610,6 @@
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -1782,153 +2624,1686 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O168"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="4" max="4" width="44.68359375" customWidth="1"/>
-    <col min="5" max="5" width="14.7890625" customWidth="1"/>
-    <col min="7" max="7" width="5.7890625" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:15" ht="30" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.7" x14ac:dyDescent="0.65">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40"/>
+    </row>
+    <row r="2" spans="1:15" ht="17">
+      <c r="A2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="16" t="s">
+      <c r="B2" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="15" t="s">
+      <c r="G2" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="43"/>
+    </row>
+    <row r="3" spans="1:15" ht="18" thickBot="1">
+      <c r="A3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="17" t="s">
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="17" t="s">
+      <c r="G3" s="57">
+        <v>45594</v>
+      </c>
+      <c r="H3" s="44"/>
+      <c r="I3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="J3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="58"/>
+    </row>
+    <row r="4" spans="1:15" ht="15">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="O4" s="58"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="O5" s="58"/>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="60"/>
+      <c r="O6" s="58"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1">
+      <c r="A7" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.35" x14ac:dyDescent="0.4">
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="D7" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="62"/>
+      <c r="O7" s="58"/>
+    </row>
+    <row r="8" spans="1:15" ht="15" customHeight="1">
+      <c r="A8" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="62"/>
+      <c r="O8" s="58"/>
+    </row>
+    <row r="9" spans="1:15" ht="15" customHeight="1">
+      <c r="A9" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="62"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1">
+      <c r="A10" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="62"/>
+      <c r="O10" s="58"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1">
+      <c r="A11" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="64"/>
+      <c r="O11" s="58"/>
+    </row>
+    <row r="12" spans="1:15" ht="15" customHeight="1">
+      <c r="A12" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="64"/>
+      <c r="O12" s="58"/>
+    </row>
+    <row r="13" spans="1:15" ht="15" customHeight="1">
+      <c r="A13" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="64"/>
+      <c r="O13" s="58"/>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1">
+      <c r="A14" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="J14" s="64"/>
+      <c r="O14" s="58"/>
+    </row>
+    <row r="15" spans="1:15" ht="15" customHeight="1">
+      <c r="A15" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="64"/>
+      <c r="O15" s="58"/>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1">
+      <c r="A16" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="66"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" customHeight="1">
+      <c r="A17" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="J17" s="66"/>
+      <c r="O17" s="58"/>
+    </row>
+    <row r="18" spans="1:15" ht="15" customHeight="1">
+      <c r="A18" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="66"/>
+      <c r="O18" s="58"/>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1">
+      <c r="A19" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="66"/>
+      <c r="O19" s="58"/>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1">
+      <c r="A20" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="66"/>
+    </row>
+    <row r="21" spans="1:15" ht="15" customHeight="1">
+      <c r="A21" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" s="66" t="s">
+        <v>140</v>
+      </c>
+      <c r="J21" s="66"/>
+      <c r="O21" s="58"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1">
+      <c r="A22" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="68"/>
+      <c r="O22" s="58"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" customHeight="1">
+      <c r="A23" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="J23" s="68"/>
+      <c r="O23" s="58"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" customHeight="1">
+      <c r="A24" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="68"/>
+      <c r="O24" s="58"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" customHeight="1">
+      <c r="A25" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="68"/>
+      <c r="O25" s="58"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" customHeight="1">
+      <c r="A26" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="E26" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="J26" s="68"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" customHeight="1">
+      <c r="A27" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="J27" s="68"/>
+      <c r="O27" s="58"/>
+    </row>
+    <row r="28" spans="1:15" ht="15" customHeight="1">
+      <c r="A28" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" s="68"/>
+      <c r="O28" s="58"/>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1">
+      <c r="A29" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" s="68"/>
+      <c r="O29" s="58"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1">
+      <c r="A30" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="J30" s="68"/>
+      <c r="O30" s="58"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" customHeight="1">
+      <c r="A31" s="69" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="69" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="I31" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="J31" s="70"/>
+      <c r="O31" s="58"/>
+    </row>
+    <row r="32" spans="1:15" ht="15" customHeight="1">
+      <c r="A32" s="69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="70"/>
+      <c r="O32" s="58"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" customHeight="1">
+      <c r="A33" s="69" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="69" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="H33" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" s="69" t="s">
+        <v>191</v>
+      </c>
+      <c r="J33" s="70"/>
+      <c r="O33" s="58"/>
+    </row>
+    <row r="34" spans="1:15" ht="15" customHeight="1">
+      <c r="A34" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="69" t="s">
+        <v>194</v>
+      </c>
+      <c r="E34" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="I34" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="70"/>
+      <c r="O34" s="58"/>
+    </row>
+    <row r="35" spans="1:15" ht="15" customHeight="1">
+      <c r="A35" s="69" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="I35" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="J35" s="70"/>
+      <c r="O35" s="58"/>
+    </row>
+    <row r="36" spans="1:15" ht="15" customHeight="1">
+      <c r="A36" s="71" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="J36" s="72"/>
+      <c r="O36" s="58"/>
+    </row>
+    <row r="37" spans="1:15" ht="15" customHeight="1">
+      <c r="A37" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="71" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="71" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="J37" s="72"/>
+      <c r="O37" s="58"/>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1">
+      <c r="A38" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="J38" s="72"/>
+      <c r="O38" s="58"/>
+    </row>
+    <row r="39" spans="1:15" ht="15" customHeight="1">
+      <c r="A39" s="71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" s="71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="71" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="H39" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I39" s="71" t="s">
+        <v>215</v>
+      </c>
+      <c r="J39" s="72"/>
+      <c r="O39" s="58"/>
+    </row>
+    <row r="40" spans="1:15" ht="15" customHeight="1">
+      <c r="A40" s="71" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="G40" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="H40" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I40" s="71" t="s">
+        <v>220</v>
+      </c>
+      <c r="J40" s="72"/>
+      <c r="O40" s="58"/>
+    </row>
+    <row r="41" spans="1:15" ht="15" customHeight="1">
+      <c r="A41" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="I41" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="J41" s="74"/>
+      <c r="O41" s="58"/>
+    </row>
+    <row r="42" spans="1:15" ht="15" customHeight="1">
+      <c r="A42" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="H42" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="I42" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="74"/>
+      <c r="O42" s="58"/>
+    </row>
+    <row r="43" spans="1:15" ht="15" customHeight="1">
+      <c r="A43" s="73" t="s">
+        <v>229</v>
+      </c>
+      <c r="B43" s="73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="73" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="73" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="I43" s="73" t="s">
+        <v>233</v>
+      </c>
+      <c r="J43" s="74"/>
+      <c r="O43" s="58"/>
+    </row>
+    <row r="44" spans="1:15" ht="15" customHeight="1">
+      <c r="A44" s="73" t="s">
+        <v>234</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="C44" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="73" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="I44" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="J44" s="74"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" customHeight="1">
+      <c r="A45" s="73" t="s">
+        <v>237</v>
+      </c>
+      <c r="B45" s="73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C45" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="73" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="H45" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="I45" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="J45" s="74"/>
+      <c r="O45" s="58"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" customHeight="1">
+      <c r="A46" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="75" t="s">
+        <v>241</v>
+      </c>
+      <c r="C46" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="75" t="s">
+        <v>242</v>
+      </c>
+      <c r="E46" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="G46" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="I46" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="J46" s="75"/>
+      <c r="O46" s="58"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" customHeight="1">
+      <c r="A47" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="75" t="s">
+        <v>245</v>
+      </c>
+      <c r="C47" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="75" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="I47" s="75" t="s">
+        <v>247</v>
+      </c>
+      <c r="J47" s="75"/>
+      <c r="O47" s="58"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" customHeight="1">
+      <c r="A48" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B48" s="75" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="75" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="75" t="s">
+        <v>251</v>
+      </c>
+      <c r="G48" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="H48" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="I48" s="75" t="s">
+        <v>252</v>
+      </c>
+      <c r="J48" s="75"/>
+      <c r="O48" s="58"/>
+    </row>
+    <row r="49" spans="1:15" ht="15" customHeight="1">
+      <c r="A49" s="75" t="s">
+        <v>253</v>
+      </c>
+      <c r="B49" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="C49" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="75" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="G49" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="H49" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="I49" s="75" t="s">
+        <v>257</v>
+      </c>
+      <c r="J49" s="75"/>
+      <c r="O49" s="58"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" customHeight="1">
+      <c r="A50" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C50" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="76" t="s">
+        <v>260</v>
+      </c>
+      <c r="E50" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="H50" s="76" t="s">
+        <v>98</v>
+      </c>
+      <c r="I50" s="76" t="s">
+        <v>261</v>
+      </c>
+      <c r="J50" s="76"/>
+      <c r="O50" s="58"/>
+    </row>
+    <row r="51" spans="1:15" ht="15" customHeight="1">
+      <c r="A51" s="76" t="s">
+        <v>262</v>
+      </c>
+      <c r="B51" s="76" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="76" t="s">
+        <v>264</v>
+      </c>
+      <c r="E51" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="H51" s="76" t="s">
+        <v>98</v>
+      </c>
+      <c r="I51" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="J51" s="76"/>
+    </row>
+    <row r="52" spans="1:15" ht="15" customHeight="1">
+      <c r="A52" s="77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" s="77" t="s">
+        <v>268</v>
+      </c>
+      <c r="E52" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="G52" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="I52" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="J52" s="77"/>
+      <c r="O52" s="58"/>
+    </row>
+    <row r="53" spans="1:15" ht="15" customHeight="1">
+      <c r="A53" s="77" t="s">
+        <v>270</v>
+      </c>
+      <c r="B53" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="77" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="G53" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="I53" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="J53" s="77"/>
+      <c r="O53" s="58"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" customHeight="1">
+      <c r="A54" s="77" t="s">
+        <v>275</v>
+      </c>
+      <c r="B54" s="77" t="s">
+        <v>276</v>
+      </c>
+      <c r="C54" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="77" t="s">
+        <v>277</v>
+      </c>
+      <c r="E54" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="H54" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="I54" s="77" t="s">
+        <v>278</v>
+      </c>
+      <c r="J54" s="77"/>
+      <c r="O54" s="58"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1">
+      <c r="A55" s="78" t="s">
+        <v>279</v>
+      </c>
+      <c r="B55" s="78" t="s">
+        <v>280</v>
+      </c>
+      <c r="C55" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="78" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="G55" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="I55" s="78" t="s">
+        <v>243</v>
+      </c>
+      <c r="J55" s="78"/>
+      <c r="O55" s="58"/>
+    </row>
+    <row r="62" spans="1:15" ht="15">
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+    </row>
+    <row r="163" spans="15:15" ht="15">
+      <c r="O163" s="59"/>
+    </row>
+    <row r="164" spans="15:15" ht="15">
+      <c r="O164" s="59"/>
+    </row>
+    <row r="165" spans="15:15" ht="15">
+      <c r="O165" s="59"/>
+    </row>
+    <row r="167" spans="15:15" ht="15">
+      <c r="O167" s="59"/>
+    </row>
+    <row r="168" spans="15:15" ht="15">
+      <c r="O168" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1951,1032 +4326,1084 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J88"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="10" max="10" width="5.578125" customWidth="1"/>
+    <col min="10" max="10" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:10" ht="20.25" customHeight="1">
+      <c r="A1" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="51"/>
+    </row>
+    <row r="3" spans="1:10" ht="6" customHeight="1"/>
+    <row r="4" spans="1:10" s="28" customFormat="1">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10" s="28" customFormat="1">
+      <c r="A5" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.7" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59"/>
-    </row>
-    <row r="3" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-    </row>
-    <row r="5" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="53" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+    </row>
+    <row r="6" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A6" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-    </row>
-    <row r="6" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+    </row>
+    <row r="7" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A7" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-    </row>
-    <row r="7" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="52" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+    </row>
+    <row r="8" spans="1:10" s="28" customFormat="1">
+      <c r="A8" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-    </row>
-    <row r="8" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="53" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+    </row>
+    <row r="9" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A9" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-    </row>
-    <row r="9" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="51" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+    </row>
+    <row r="10" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A10" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-    </row>
-    <row r="10" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="52" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+    </row>
+    <row r="11" spans="1:10" s="28" customFormat="1">
+      <c r="A11" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="53" t="s">
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+    </row>
+    <row r="12" spans="1:10" s="28" customFormat="1">
+      <c r="A12" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-    </row>
-    <row r="12" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="50" t="s">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" spans="1:10" s="28" customFormat="1">
+      <c r="A13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-    </row>
-    <row r="13" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="50" t="s">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+    </row>
+    <row r="14" spans="1:10" s="28" customFormat="1">
+      <c r="A14" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="50" t="s">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+    </row>
+    <row r="15" spans="1:10" s="28" customFormat="1">
+      <c r="A15" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-    </row>
-    <row r="15" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="50" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+    </row>
+    <row r="16" spans="1:10" s="28" customFormat="1">
+      <c r="A16" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-    </row>
-    <row r="16" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="50" t="s">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+    </row>
+    <row r="17" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A17" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-    </row>
-    <row r="17" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51" t="s">
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+    </row>
+    <row r="18" spans="1:10" s="28" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A18" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" spans="1:10" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="52" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="19" spans="1:10" s="28" customFormat="1">
+      <c r="A19" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-    </row>
-    <row r="19" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="50" t="s">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+    </row>
+    <row r="20" spans="1:10" s="28" customFormat="1">
+      <c r="A20" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-    </row>
-    <row r="20" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="50" t="s">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+    </row>
+    <row r="21" spans="1:10" s="28" customFormat="1">
+      <c r="A21" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-    </row>
-    <row r="21" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="50" t="s">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+    </row>
+    <row r="22" spans="1:10" s="28" customFormat="1">
+      <c r="A22" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-    </row>
-    <row r="22" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="50" t="s">
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+    </row>
+    <row r="23" spans="1:10" s="28" customFormat="1">
+      <c r="A23" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-    </row>
-    <row r="23" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="50" t="s">
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+    </row>
+    <row r="24" spans="1:10" s="28" customFormat="1">
+      <c r="A24" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-    </row>
-    <row r="24" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="50" t="s">
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+    </row>
+    <row r="25" spans="1:10" s="28" customFormat="1">
+      <c r="A25" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-    </row>
-    <row r="25" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="50" t="s">
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
+    </row>
+    <row r="26" spans="1:10" s="28" customFormat="1">
+      <c r="A26" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-    </row>
-    <row r="26" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="50" t="s">
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+    </row>
+    <row r="27" spans="1:10" s="28" customFormat="1">
+      <c r="A27" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-    </row>
-    <row r="27" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="50" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+    </row>
+    <row r="28" spans="1:10" s="28" customFormat="1">
+      <c r="A28" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-    </row>
-    <row r="28" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="50" t="s">
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+    </row>
+    <row r="29" spans="1:10" s="28" customFormat="1">
+      <c r="A29" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-    </row>
-    <row r="29" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="50" t="s">
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+    </row>
+    <row r="30" spans="1:10" s="28" customFormat="1">
+      <c r="A30" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-    </row>
-    <row r="30" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="50" t="s">
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+    </row>
+    <row r="31" spans="1:10" s="28" customFormat="1">
+      <c r="A31" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-    </row>
-    <row r="31" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="50" t="s">
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+    </row>
+    <row r="32" spans="1:10" s="28" customFormat="1">
+      <c r="A32" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-    </row>
-    <row r="32" spans="1:10" s="29" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-    </row>
-    <row r="33" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A33" s="30"/>
-    </row>
-    <row r="34" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A35" s="30"/>
-    </row>
-    <row r="36" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A36" s="30"/>
-    </row>
-    <row r="37" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A37" s="30"/>
-    </row>
-    <row r="38" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A38" s="30"/>
-    </row>
-    <row r="39" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A39" s="30"/>
-    </row>
-    <row r="40" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A40" s="30"/>
-    </row>
-    <row r="41" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A41" s="30"/>
-    </row>
-    <row r="42" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A42" s="30"/>
-    </row>
-    <row r="43" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A43" s="49"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-    </row>
-    <row r="44" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A44" s="49"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-    </row>
-    <row r="45" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A45" s="49"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-    </row>
-    <row r="46" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A46" s="49"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="49"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-    </row>
-    <row r="47" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-    </row>
-    <row r="48" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-    </row>
-    <row r="49" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A49" s="49"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
-    </row>
-    <row r="50" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A50" s="49"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="49"/>
-    </row>
-    <row r="51" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A51" s="49"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="49"/>
-    </row>
-    <row r="52" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A52" s="49"/>
-      <c r="B52" s="49"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-    </row>
-    <row r="53" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A53" s="49"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="49"/>
-    </row>
-    <row r="54" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="49"/>
-    </row>
-    <row r="55" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A55" s="49"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-    </row>
-    <row r="56" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A56" s="49"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="49"/>
-    </row>
-    <row r="57" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A57" s="49"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="49"/>
-    </row>
-    <row r="58" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-    </row>
-    <row r="59" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-    </row>
-    <row r="60" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="49"/>
-    </row>
-    <row r="61" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-    </row>
-    <row r="62" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="G62" s="49"/>
-      <c r="H62" s="49"/>
-      <c r="I62" s="49"/>
-      <c r="J62" s="49"/>
-    </row>
-    <row r="63" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A63" s="49"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-    </row>
-    <row r="64" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A64" s="49"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="49"/>
-      <c r="I64" s="49"/>
-      <c r="J64" s="49"/>
-    </row>
-    <row r="65" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A65" s="49"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49"/>
-      <c r="D65" s="49"/>
-      <c r="E65" s="49"/>
-      <c r="F65" s="49"/>
-      <c r="G65" s="49"/>
-      <c r="H65" s="49"/>
-      <c r="I65" s="49"/>
-      <c r="J65" s="49"/>
-    </row>
-    <row r="66" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A66" s="49"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49"/>
-      <c r="D66" s="49"/>
-      <c r="E66" s="49"/>
-      <c r="F66" s="49"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="49"/>
-      <c r="I66" s="49"/>
-      <c r="J66" s="49"/>
-    </row>
-    <row r="67" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A67" s="49"/>
-      <c r="B67" s="49"/>
-      <c r="C67" s="49"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="49"/>
-      <c r="F67" s="49"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="49"/>
-      <c r="I67" s="49"/>
-      <c r="J67" s="49"/>
-    </row>
-    <row r="68" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A68" s="49"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
-      <c r="D68" s="49"/>
-      <c r="E68" s="49"/>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49"/>
-      <c r="J68" s="49"/>
-    </row>
-    <row r="69" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A69" s="49"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49"/>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="49"/>
-      <c r="J69" s="49"/>
-    </row>
-    <row r="70" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A70" s="49"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="49"/>
-    </row>
-    <row r="71" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A71" s="49"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49"/>
-      <c r="J71" s="49"/>
-    </row>
-    <row r="72" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A72" s="49"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49"/>
-      <c r="J72" s="49"/>
-    </row>
-    <row r="73" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A73" s="49"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49"/>
-      <c r="J73" s="49"/>
-    </row>
-    <row r="74" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A74" s="49"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49"/>
-      <c r="J74" s="49"/>
-    </row>
-    <row r="75" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
-      <c r="J75" s="49"/>
-    </row>
-    <row r="76" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
-      <c r="J76" s="49"/>
-    </row>
-    <row r="77" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A77" s="49"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="49"/>
-      <c r="D77" s="49"/>
-      <c r="E77" s="49"/>
-      <c r="F77" s="49"/>
-      <c r="G77" s="49"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="49"/>
-      <c r="J77" s="49"/>
-    </row>
-    <row r="78" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="49"/>
-    </row>
-    <row r="79" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="49"/>
-    </row>
-    <row r="80" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
-      <c r="J80" s="49"/>
-    </row>
-    <row r="81" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A81" s="49"/>
-      <c r="B81" s="49"/>
-      <c r="C81" s="49"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="49"/>
-      <c r="J81" s="49"/>
-    </row>
-    <row r="82" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A82" s="49"/>
-      <c r="B82" s="49"/>
-      <c r="C82" s="49"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
-      <c r="H82" s="49"/>
-      <c r="I82" s="49"/>
-      <c r="J82" s="49"/>
-    </row>
-    <row r="83" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A83" s="49"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="49"/>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="49"/>
-      <c r="G83" s="49"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="49"/>
-    </row>
-    <row r="84" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A84" s="49"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="49"/>
-    </row>
-    <row r="85" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A85" s="49"/>
-      <c r="B85" s="49"/>
-      <c r="C85" s="49"/>
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="G85" s="49"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="49"/>
-      <c r="J85" s="49"/>
-    </row>
-    <row r="86" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A86" s="49"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="49"/>
-      <c r="J86" s="49"/>
-    </row>
-    <row r="87" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="49"/>
-    </row>
-    <row r="88" spans="1:10" s="29" customFormat="1" ht="12.35" x14ac:dyDescent="0.3">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
-      <c r="J88" s="49"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+    </row>
+    <row r="33" spans="1:10" s="28" customFormat="1">
+      <c r="A33" s="29"/>
+    </row>
+    <row r="34" spans="1:10" s="28" customFormat="1">
+      <c r="A34" s="29"/>
+    </row>
+    <row r="35" spans="1:10" s="28" customFormat="1">
+      <c r="A35" s="29"/>
+    </row>
+    <row r="36" spans="1:10" s="28" customFormat="1">
+      <c r="A36" s="29"/>
+    </row>
+    <row r="37" spans="1:10" s="28" customFormat="1">
+      <c r="A37" s="29"/>
+    </row>
+    <row r="38" spans="1:10" s="28" customFormat="1">
+      <c r="A38" s="29"/>
+    </row>
+    <row r="39" spans="1:10" s="28" customFormat="1">
+      <c r="A39" s="29"/>
+    </row>
+    <row r="40" spans="1:10" s="28" customFormat="1">
+      <c r="A40" s="29"/>
+    </row>
+    <row r="41" spans="1:10" s="28" customFormat="1">
+      <c r="A41" s="29"/>
+    </row>
+    <row r="42" spans="1:10" s="28" customFormat="1">
+      <c r="A42" s="29"/>
+    </row>
+    <row r="43" spans="1:10" s="28" customFormat="1">
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
+    </row>
+    <row r="44" spans="1:10" s="28" customFormat="1">
+      <c r="A44" s="56"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+    </row>
+    <row r="45" spans="1:10" s="28" customFormat="1">
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+    </row>
+    <row r="46" spans="1:10" s="28" customFormat="1">
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
+    </row>
+    <row r="47" spans="1:10" s="28" customFormat="1">
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="56"/>
+    </row>
+    <row r="48" spans="1:10" s="28" customFormat="1">
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="56"/>
+    </row>
+    <row r="49" spans="1:10" s="28" customFormat="1">
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+    </row>
+    <row r="50" spans="1:10" s="28" customFormat="1">
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
+    </row>
+    <row r="51" spans="1:10" s="28" customFormat="1">
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+    </row>
+    <row r="52" spans="1:10" s="28" customFormat="1">
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+    </row>
+    <row r="53" spans="1:10" s="28" customFormat="1">
+      <c r="A53" s="56"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+    </row>
+    <row r="54" spans="1:10" s="28" customFormat="1">
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="56"/>
+    </row>
+    <row r="55" spans="1:10" s="28" customFormat="1">
+      <c r="A55" s="56"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="56"/>
+    </row>
+    <row r="56" spans="1:10" s="28" customFormat="1">
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
+    </row>
+    <row r="57" spans="1:10" s="28" customFormat="1">
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="56"/>
+    </row>
+    <row r="58" spans="1:10" s="28" customFormat="1">
+      <c r="A58" s="56"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
+    </row>
+    <row r="59" spans="1:10" s="28" customFormat="1">
+      <c r="A59" s="56"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="56"/>
+    </row>
+    <row r="60" spans="1:10" s="28" customFormat="1">
+      <c r="A60" s="56"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="56"/>
+    </row>
+    <row r="61" spans="1:10" s="28" customFormat="1">
+      <c r="A61" s="56"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+    </row>
+    <row r="62" spans="1:10" s="28" customFormat="1">
+      <c r="A62" s="56"/>
+      <c r="B62" s="56"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="56"/>
+    </row>
+    <row r="63" spans="1:10" s="28" customFormat="1">
+      <c r="A63" s="56"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="56"/>
+    </row>
+    <row r="64" spans="1:10" s="28" customFormat="1">
+      <c r="A64" s="56"/>
+      <c r="B64" s="56"/>
+      <c r="C64" s="56"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="56"/>
+    </row>
+    <row r="65" spans="1:10" s="28" customFormat="1">
+      <c r="A65" s="56"/>
+      <c r="B65" s="56"/>
+      <c r="C65" s="56"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="56"/>
+    </row>
+    <row r="66" spans="1:10" s="28" customFormat="1">
+      <c r="A66" s="56"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="56"/>
+    </row>
+    <row r="67" spans="1:10" s="28" customFormat="1">
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="56"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="56"/>
+    </row>
+    <row r="68" spans="1:10" s="28" customFormat="1">
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
+      <c r="H68" s="56"/>
+      <c r="I68" s="56"/>
+      <c r="J68" s="56"/>
+    </row>
+    <row r="69" spans="1:10" s="28" customFormat="1">
+      <c r="A69" s="56"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
+      <c r="H69" s="56"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="56"/>
+    </row>
+    <row r="70" spans="1:10" s="28" customFormat="1">
+      <c r="A70" s="56"/>
+      <c r="B70" s="56"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="56"/>
+    </row>
+    <row r="71" spans="1:10" s="28" customFormat="1">
+      <c r="A71" s="56"/>
+      <c r="B71" s="56"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="56"/>
+      <c r="F71" s="56"/>
+      <c r="G71" s="56"/>
+      <c r="H71" s="56"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="56"/>
+    </row>
+    <row r="72" spans="1:10" s="28" customFormat="1">
+      <c r="A72" s="56"/>
+      <c r="B72" s="56"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="56"/>
+      <c r="F72" s="56"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="56"/>
+    </row>
+    <row r="73" spans="1:10" s="28" customFormat="1">
+      <c r="A73" s="56"/>
+      <c r="B73" s="56"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="56"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="56"/>
+    </row>
+    <row r="74" spans="1:10" s="28" customFormat="1">
+      <c r="A74" s="56"/>
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="56"/>
+    </row>
+    <row r="75" spans="1:10" s="28" customFormat="1">
+      <c r="A75" s="56"/>
+      <c r="B75" s="56"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="56"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="56"/>
+    </row>
+    <row r="76" spans="1:10" s="28" customFormat="1">
+      <c r="A76" s="56"/>
+      <c r="B76" s="56"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="56"/>
+    </row>
+    <row r="77" spans="1:10" s="28" customFormat="1">
+      <c r="A77" s="56"/>
+      <c r="B77" s="56"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+    </row>
+    <row r="78" spans="1:10" s="28" customFormat="1">
+      <c r="A78" s="56"/>
+      <c r="B78" s="56"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="56"/>
+      <c r="F78" s="56"/>
+      <c r="G78" s="56"/>
+      <c r="H78" s="56"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="56"/>
+    </row>
+    <row r="79" spans="1:10" s="28" customFormat="1">
+      <c r="A79" s="56"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="56"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="56"/>
+    </row>
+    <row r="80" spans="1:10" s="28" customFormat="1">
+      <c r="A80" s="56"/>
+      <c r="B80" s="56"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="56"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="56"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="56"/>
+    </row>
+    <row r="81" spans="1:10" s="28" customFormat="1">
+      <c r="A81" s="56"/>
+      <c r="B81" s="56"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56"/>
+      <c r="J81" s="56"/>
+    </row>
+    <row r="82" spans="1:10" s="28" customFormat="1">
+      <c r="A82" s="56"/>
+      <c r="B82" s="56"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="56"/>
+    </row>
+    <row r="83" spans="1:10" s="28" customFormat="1">
+      <c r="A83" s="56"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="56"/>
+      <c r="E83" s="56"/>
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="56"/>
+    </row>
+    <row r="84" spans="1:10" s="28" customFormat="1">
+      <c r="A84" s="56"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="56"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="56"/>
+    </row>
+    <row r="85" spans="1:10" s="28" customFormat="1">
+      <c r="A85" s="56"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+    </row>
+    <row r="86" spans="1:10" s="28" customFormat="1">
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="56"/>
+      <c r="J86" s="56"/>
+    </row>
+    <row r="87" spans="1:10" s="28" customFormat="1">
+      <c r="A87" s="56"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="56"/>
+      <c r="D87" s="56"/>
+      <c r="E87" s="56"/>
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="56"/>
+      <c r="J87" s="56"/>
+    </row>
+    <row r="88" spans="1:10" s="28" customFormat="1">
+      <c r="A88" s="56"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="56"/>
+      <c r="D88" s="56"/>
+      <c r="E88" s="56"/>
+      <c r="F88" s="56"/>
+      <c r="G88" s="56"/>
+      <c r="H88" s="56"/>
+      <c r="I88" s="56"/>
+      <c r="J88" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A85:J85"/>
+    <mergeCell ref="A86:J86"/>
+    <mergeCell ref="A87:J87"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A10:J10"/>
@@ -2989,64 +5416,12 @@
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A85:J85"/>
-    <mergeCell ref="A86:J86"/>
-    <mergeCell ref="A87:J87"/>
-    <mergeCell ref="A88:J88"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A80:J80"/>
-    <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
